--- a/Auditoria_Reabilitacao_Inidoneidade/05_Entregaveis/Planilha_JDS_Reavaliada_113_Questoes.xlsx
+++ b/Auditoria_Reabilitacao_Inidoneidade/05_Entregaveis/Planilha_JDS_Reavaliada_113_Questoes.xlsx
@@ -1140,7 +1140,6 @@
       <c r="F2" s="81" t="n"/>
       <c r="G2" s="82" t="n"/>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="83" t="inlineStr">
         <is>
